--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3088FAB-4973-4802-9014-CEB2D2F92E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E755B47-6B5A-4E1C-80DF-F51D80A06818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -275,7 +275,7 @@
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,6 +388,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -741,7 +749,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -841,9 +849,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1074,6 +1079,37 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1802,22 +1838,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="2"/>
-    <col min="2" max="2" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="2"/>
+    <col min="2" max="2" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="2"/>
-    <col min="10" max="10" width="9.28515625" style="14"/>
-    <col min="11" max="16384" width="9.28515625" style="2"/>
+    <col min="6" max="6" width="38.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="134"/>
+    <col min="10" max="10" width="9.33203125" style="14"/>
+    <col min="11" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1839,183 +1875,195 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="131"/>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="77"/>
-      <c r="B2" s="41" t="s">
+    <row r="2" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="124" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="126">
         <v>0.2</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="127">
         <v>46242</v>
       </c>
-      <c r="F2" s="45">
+      <c r="F2" s="128">
         <v>46264</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47" t="s">
+      <c r="G2" s="129"/>
+      <c r="H2" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="103" t="s">
+      <c r="I2" s="132"/>
+      <c r="J2" s="109"/>
+    </row>
+    <row r="3" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="105">
+      <c r="D3" s="104">
         <v>0.2</v>
       </c>
-      <c r="E3" s="106">
+      <c r="E3" s="105">
         <v>46246</v>
       </c>
-      <c r="F3" s="107"/>
-      <c r="G3" s="108">
+      <c r="F3" s="106"/>
+      <c r="G3" s="107">
         <v>0.99930555555555556</v>
       </c>
-      <c r="H3" s="109" t="s">
+      <c r="H3" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="110"/>
-    </row>
-    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="56" t="s">
+      <c r="I3" s="132"/>
+      <c r="J3" s="109"/>
+    </row>
+    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="57">
         <v>0.15</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="58">
         <v>46249</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="59">
         <v>46292</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="62" t="s">
+      <c r="G4" s="60"/>
+      <c r="H4" s="61" t="s">
         <v>26</v>
       </c>
+      <c r="I4" s="133">
+        <v>7</v>
+      </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="63" t="s">
+    <row r="5" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="104">
         <v>0.1</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="105">
         <v>46251</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="106">
         <v>46257</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55" t="s">
+      <c r="G5" s="107"/>
+      <c r="H5" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="16"/>
-    </row>
-    <row r="6" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="118" t="s">
+      <c r="I5" s="132"/>
+      <c r="J5" s="109"/>
+    </row>
+    <row r="6" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="120">
+      <c r="D6" s="119">
         <v>0.1</v>
       </c>
-      <c r="E6" s="121">
+      <c r="E6" s="120">
         <v>46251</v>
       </c>
-      <c r="F6" s="122">
+      <c r="F6" s="121">
         <v>46257</v>
       </c>
-      <c r="G6" s="123"/>
-      <c r="H6" s="124"/>
-      <c r="J6" s="110"/>
-    </row>
-    <row r="7" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="111" t="s">
+      <c r="G6" s="122"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="109"/>
+    </row>
+    <row r="7" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="113">
+      <c r="D7" s="112">
         <v>0.1</v>
       </c>
-      <c r="E7" s="114">
+      <c r="E7" s="113">
         <v>46253</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="116">
+      <c r="F7" s="114"/>
+      <c r="G7" s="115">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H7" s="117" t="s">
+      <c r="H7" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="110"/>
-    </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="68" t="s">
+      <c r="I7" s="132"/>
+      <c r="J7" s="109"/>
+    </row>
+    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="42">
         <v>0.1</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="43">
         <v>46266</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="44">
         <v>46353</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="133"/>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="63" t="s">
+    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="50">
         <v>0.15</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="51">
         <v>46272</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54">
+      <c r="F9" s="52"/>
+      <c r="G9" s="53">
         <v>0.875</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="54" t="s">
         <v>30</v>
       </c>
+      <c r="I9" s="133">
+        <v>1</v>
+      </c>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="64" t="s">
+    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B10" s="63" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="25" t="s">
@@ -2031,11 +2079,14 @@
         <v>46278</v>
       </c>
       <c r="G10" s="29"/>
-      <c r="H10" s="65"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="133">
+        <v>4</v>
+      </c>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="69" t="s">
+    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="25" t="s">
@@ -2051,365 +2102,396 @@
       <c r="G11" s="29">
         <v>0.875</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="64" t="s">
         <v>21</v>
       </c>
+      <c r="I11" s="133">
+        <v>3</v>
+      </c>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="66" t="s">
+    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="57">
         <v>0.15</v>
       </c>
-      <c r="E12" s="67">
+      <c r="E12" s="66">
         <v>46274</v>
       </c>
-      <c r="F12" s="60"/>
-      <c r="G12" s="61">
+      <c r="F12" s="59"/>
+      <c r="G12" s="60">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="61" t="s">
         <v>28</v>
       </c>
+      <c r="I12" s="133">
+        <v>2</v>
+      </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="77"/>
-      <c r="B13" s="68" t="s">
+    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="76"/>
+      <c r="B13" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="42">
         <v>0.1</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="43">
         <v>46279</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="44">
         <v>46285</v>
       </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47" t="s">
+      <c r="G13" s="45"/>
+      <c r="H13" s="46" t="s">
         <v>37</v>
       </c>
+      <c r="I13" s="133">
+        <v>5</v>
+      </c>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="70" t="s">
+    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="50">
         <v>0.1</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="70">
         <v>46288</v>
       </c>
-      <c r="F14" s="53"/>
-      <c r="G14" s="54">
+      <c r="F14" s="52"/>
+      <c r="G14" s="53">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="54" t="s">
         <v>28</v>
       </c>
+      <c r="I14" s="133">
+        <v>6</v>
+      </c>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="72" t="s">
+    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="57">
         <v>0.1</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="58">
         <v>46290</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="59">
         <v>46297</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="133">
+        <v>9</v>
+      </c>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="49" t="s">
+    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="50">
         <v>0.2</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="51">
         <v>46295</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="54">
+      <c r="F16" s="52"/>
+      <c r="G16" s="53">
         <v>0.875</v>
       </c>
-      <c r="H16" s="55" t="s">
+      <c r="H16" s="54" t="s">
         <v>17</v>
       </c>
+      <c r="I16" s="133">
+        <v>8</v>
+      </c>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="56" t="s">
+    <row r="17" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="57">
         <v>0.3</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="58">
         <v>46297</v>
       </c>
-      <c r="F17" s="60"/>
-      <c r="G17" s="61">
+      <c r="F17" s="59"/>
+      <c r="G17" s="60">
         <v>0.875</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="61" t="s">
         <v>26</v>
       </c>
+      <c r="I17" s="133">
+        <v>10</v>
+      </c>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="77"/>
-      <c r="B18" s="73" t="s">
+    <row r="18" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="76"/>
+      <c r="B18" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="50">
         <v>0.2</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="51">
         <v>46300</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="52">
         <v>46320</v>
       </c>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="133"/>
       <c r="J18" s="21"/>
     </row>
-    <row r="19" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="77"/>
-      <c r="B19" s="66" t="s">
+    <row r="19" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="76"/>
+      <c r="B19" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="74">
+      <c r="D19" s="73">
         <v>0.1</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="58">
         <v>46302</v>
       </c>
-      <c r="F19" s="60"/>
-      <c r="G19" s="61">
+      <c r="F19" s="59"/>
+      <c r="G19" s="60">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H19" s="62" t="s">
+      <c r="H19" s="61" t="s">
         <v>26</v>
       </c>
+      <c r="I19" s="133"/>
       <c r="J19" s="21"/>
     </row>
-    <row r="20" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="63" t="s">
+    <row r="20" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="50">
         <v>0.1</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="51">
         <v>46308</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="52">
         <v>46313</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="55" t="s">
+      <c r="G20" s="53"/>
+      <c r="H20" s="54" t="s">
         <v>38</v>
       </c>
+      <c r="I20" s="133"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="56" t="s">
+    <row r="21" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="57">
         <v>0.15</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E21" s="58">
         <v>46308</v>
       </c>
-      <c r="F21" s="60">
+      <c r="F21" s="59">
         <v>46327</v>
       </c>
-      <c r="G21" s="61"/>
-      <c r="H21" s="62" t="s">
+      <c r="G21" s="60"/>
+      <c r="H21" s="61" t="s">
         <v>27</v>
       </c>
+      <c r="I21" s="133"/>
       <c r="J21" s="21"/>
     </row>
-    <row r="22" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="75" t="s">
+    <row r="22" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="50">
         <v>0.2</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="51">
         <v>46315</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="52">
         <v>46344</v>
       </c>
-      <c r="G22" s="54"/>
-      <c r="H22" s="55" t="s">
+      <c r="G22" s="53"/>
+      <c r="H22" s="54" t="s">
         <v>29</v>
       </c>
+      <c r="I22" s="133"/>
       <c r="J22" s="21"/>
     </row>
-    <row r="23" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="66" t="s">
+    <row r="23" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="57">
         <v>0.1</v>
       </c>
-      <c r="E23" s="59">
+      <c r="E23" s="58">
         <v>46316</v>
       </c>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61">
+      <c r="F23" s="59"/>
+      <c r="G23" s="60">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H23" s="62" t="s">
+      <c r="H23" s="61" t="s">
         <v>56</v>
       </c>
+      <c r="I23" s="133"/>
       <c r="J23" s="21"/>
     </row>
-    <row r="24" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="77"/>
-      <c r="B24" s="49" t="s">
+    <row r="24" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="76"/>
+      <c r="B24" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="50">
         <v>0.1</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="51">
         <v>46323</v>
       </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54">
+      <c r="F24" s="52"/>
+      <c r="G24" s="53">
         <v>0.875</v>
       </c>
-      <c r="H24" s="55" t="s">
+      <c r="H24" s="54" t="s">
         <v>22</v>
       </c>
+      <c r="I24" s="133"/>
       <c r="J24" s="21"/>
     </row>
-    <row r="25" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="77"/>
-      <c r="B25" s="72" t="s">
+    <row r="25" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="76"/>
+      <c r="B25" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="57">
         <v>0.2</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="58">
         <v>46325</v>
       </c>
-      <c r="F25" s="60">
+      <c r="F25" s="59">
         <v>46341</v>
       </c>
-      <c r="G25" s="61"/>
-      <c r="H25" s="62"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="133"/>
       <c r="J25" s="21"/>
     </row>
-    <row r="26" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="76" t="s">
+    <row r="26" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="42">
         <v>0.15</v>
       </c>
-      <c r="E26" s="44">
+      <c r="E26" s="43">
         <v>46330</v>
       </c>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46">
+      <c r="F26" s="44"/>
+      <c r="G26" s="45">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="46" t="s">
         <v>51</v>
       </c>
+      <c r="I26" s="133"/>
       <c r="J26" s="21"/>
     </row>
-    <row r="27" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="63" t="s">
+    <row r="27" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="50">
         <v>0.1</v>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="51">
         <v>46335</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="52">
         <v>46341</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="55" t="s">
+      <c r="G27" s="53"/>
+      <c r="H27" s="54" t="s">
         <v>39</v>
       </c>
+      <c r="I27" s="133"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="69" t="s">
+    <row r="28" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B28" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -2425,63 +2507,66 @@
       <c r="G28" s="29">
         <v>0.49930555555555556</v>
       </c>
-      <c r="H28" s="65"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="133"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
     </row>
-    <row r="29" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="72" t="s">
+    <row r="29" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="58">
+      <c r="D29" s="57">
         <v>0.2</v>
       </c>
-      <c r="E29" s="59">
+      <c r="E29" s="58">
         <v>46336</v>
       </c>
-      <c r="F29" s="60"/>
-      <c r="G29" s="61">
+      <c r="F29" s="59"/>
+      <c r="G29" s="60">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H29" s="62" t="s">
+      <c r="H29" s="61" t="s">
         <v>41</v>
       </c>
+      <c r="I29" s="133"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
     </row>
-    <row r="30" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="77"/>
-      <c r="B30" s="63" t="s">
+    <row r="30" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="76"/>
+      <c r="B30" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="50">
         <v>0.15</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="51">
         <v>46342</v>
       </c>
-      <c r="F30" s="53"/>
-      <c r="G30" s="54">
+      <c r="F30" s="52"/>
+      <c r="G30" s="53">
         <v>0.875</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="54" t="s">
         <v>31</v>
       </c>
+      <c r="I30" s="133"/>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
     </row>
-    <row r="31" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="77"/>
-      <c r="B31" s="64" t="s">
+    <row r="31" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="76"/>
+      <c r="B31" s="63" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="25" t="s">
@@ -2497,14 +2582,15 @@
         <v>46343</v>
       </c>
       <c r="G31" s="29"/>
-      <c r="H31" s="65"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="133"/>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
     </row>
-    <row r="32" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="77"/>
-      <c r="B32" s="69" t="s">
+    <row r="32" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="76"/>
+      <c r="B32" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="25" t="s">
@@ -2520,39 +2606,41 @@
       <c r="G32" s="29">
         <v>0.875</v>
       </c>
-      <c r="H32" s="65" t="s">
+      <c r="H32" s="64" t="s">
         <v>20</v>
       </c>
+      <c r="I32" s="133"/>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="77"/>
-      <c r="B33" s="66" t="s">
+    <row r="33" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="76"/>
+      <c r="B33" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="58">
+      <c r="D33" s="57">
         <v>0.2</v>
       </c>
-      <c r="E33" s="67">
+      <c r="E33" s="66">
         <v>46344</v>
       </c>
-      <c r="F33" s="60"/>
-      <c r="G33" s="61">
+      <c r="F33" s="59"/>
+      <c r="G33" s="60">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H33" s="62" t="s">
+      <c r="H33" s="61" t="s">
         <v>57</v>
       </c>
+      <c r="I33" s="133"/>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
     </row>
-    <row r="34" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="48" t="s">
+    <row r="34" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B34" s="47" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="35" t="s">
@@ -2571,10 +2659,11 @@
       <c r="H34" s="40" t="s">
         <v>41</v>
       </c>
+      <c r="I34" s="133"/>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
     </row>
-    <row r="35" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B35" s="34" t="s">
         <v>13</v>
       </c>
@@ -2588,22 +2677,24 @@
       <c r="F35" s="28"/>
       <c r="G35" s="29"/>
       <c r="H35" s="30"/>
+      <c r="I35" s="133"/>
       <c r="J35" s="21"/>
       <c r="L35" s="21"/>
     </row>
-    <row r="36" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.5">
       <c r="B36" s="23"/>
       <c r="D36" s="12"/>
       <c r="E36" s="17"/>
       <c r="F36" s="18"/>
       <c r="G36" s="19"/>
       <c r="H36" s="24"/>
+      <c r="I36" s="133"/>
       <c r="J36" s="16"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.5">
       <c r="B37" s="3"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.5">
       <c r="B38" s="3"/>
     </row>
   </sheetData>
@@ -2626,128 +2717,128 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A4DFEF-9CFA-41F9-A8B9-C136CDE44FC9}">
   <dimension ref="B1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="D2" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="77" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+    <row r="3" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="D3" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="95" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="82" t="s">
+    <row r="4" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="C4" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="101" t="s">
+      <c r="F4" s="100" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85" t="s">
+    <row r="5" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="99" t="s">
+      <c r="C5" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="86" t="s">
+      <c r="F5" s="85" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="80" t="s">
+    <row r="6" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="94" t="s">
+      <c r="E6" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="87" t="s">
+      <c r="F6" s="86" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="97" t="s">
+    <row r="7" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="83" t="s">
+      <c r="E7" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="98" t="s">
+    <row r="8" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="82" t="s">
+      <c r="D8" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="84" t="s">
+      <c r="E8" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="84" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E755B47-6B5A-4E1C-80DF-F51D80A06818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D363271-B0B8-443A-AB0C-63EE2574E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,9 +921,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1111,6 +1108,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1848,12 +1846,12 @@
     <col min="6" max="6" width="38.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="134"/>
+    <col min="9" max="9" width="9.33203125" style="133"/>
     <col min="10" max="10" width="9.33203125" style="14"/>
     <col min="11" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1875,56 +1873,56 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="131"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="124" t="s">
+    <row r="2" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="126">
+      <c r="D2" s="125">
         <v>0.2</v>
       </c>
-      <c r="E2" s="127">
+      <c r="E2" s="126">
         <v>46242</v>
       </c>
-      <c r="F2" s="128">
+      <c r="F2" s="127">
         <v>46264</v>
       </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130" t="s">
+      <c r="G2" s="128"/>
+      <c r="H2" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="132"/>
-      <c r="J2" s="109"/>
-    </row>
-    <row r="3" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="102" t="s">
+      <c r="I2" s="131"/>
+      <c r="J2" s="108"/>
+    </row>
+    <row r="3" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="104">
+      <c r="D3" s="103">
         <v>0.2</v>
       </c>
-      <c r="E3" s="105">
+      <c r="E3" s="104">
         <v>46246</v>
       </c>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107">
+      <c r="F3" s="105"/>
+      <c r="G3" s="106">
         <v>0.99930555555555556</v>
       </c>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="132"/>
-      <c r="J3" s="109"/>
-    </row>
-    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="I3" s="131"/>
+      <c r="J3" s="108"/>
+    </row>
+    <row r="4" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="55" t="s">
         <v>14</v>
       </c>
@@ -1944,225 +1942,214 @@
       <c r="H4" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="133">
+      <c r="I4" s="132">
+        <v>1</v>
+      </c>
+      <c r="J4" s="16"/>
+    </row>
+    <row r="5" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="103">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="104">
+        <v>46251</v>
+      </c>
+      <c r="F5" s="105">
+        <v>46257</v>
+      </c>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="131"/>
+      <c r="J5" s="108"/>
+    </row>
+    <row r="6" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="118">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="119">
+        <v>46251</v>
+      </c>
+      <c r="F6" s="120">
+        <v>46257</v>
+      </c>
+      <c r="G6" s="121"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="108"/>
+    </row>
+    <row r="7" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="111">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="112">
+        <v>46253</v>
+      </c>
+      <c r="F7" s="113"/>
+      <c r="G7" s="114">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H7" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="131"/>
+      <c r="J7" s="108"/>
+    </row>
+    <row r="8" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="124" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="125">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="126">
+        <v>46266</v>
+      </c>
+      <c r="F8" s="127">
+        <v>46353</v>
+      </c>
+      <c r="G8" s="128"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="108"/>
+    </row>
+    <row r="9" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="102" t="s">
+      <c r="D9" s="103">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="104">
+        <v>46272</v>
+      </c>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106">
+        <v>0.875</v>
+      </c>
+      <c r="H9" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="131"/>
+      <c r="J9" s="108"/>
+    </row>
+    <row r="10" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B10" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="E10" s="119">
+        <v>46272</v>
+      </c>
+      <c r="F10" s="120">
+        <v>46278</v>
+      </c>
+      <c r="G10" s="121"/>
+      <c r="H10" s="122"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="108"/>
+    </row>
+    <row r="11" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="118">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="119">
+        <v>46274</v>
+      </c>
+      <c r="F11" s="120"/>
+      <c r="G11" s="121">
+        <v>0.875</v>
+      </c>
+      <c r="H11" s="122" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="131"/>
+      <c r="J11" s="108"/>
+    </row>
+    <row r="12" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="111">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="112">
+        <v>46274</v>
+      </c>
+      <c r="F12" s="113"/>
+      <c r="G12" s="114">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H12" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="131"/>
+      <c r="J12" s="108"/>
+    </row>
+    <row r="13" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="103" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="104">
+      <c r="C13" s="124" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="125">
         <v>0.1</v>
       </c>
-      <c r="E5" s="105">
-        <v>46251</v>
-      </c>
-      <c r="F5" s="106">
-        <v>46257</v>
-      </c>
-      <c r="G5" s="107"/>
-      <c r="H5" s="108" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="132"/>
-      <c r="J5" s="109"/>
-    </row>
-    <row r="6" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="117" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="118" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="119">
-        <v>0.1</v>
-      </c>
-      <c r="E6" s="120">
-        <v>46251</v>
-      </c>
-      <c r="F6" s="121">
-        <v>46257</v>
-      </c>
-      <c r="G6" s="122"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="109"/>
-    </row>
-    <row r="7" spans="1:10" s="101" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="110" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="111" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="112">
-        <v>0.1</v>
-      </c>
-      <c r="E7" s="113">
-        <v>46253</v>
-      </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="115">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H7" s="116" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="132"/>
-      <c r="J7" s="109"/>
-    </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="42">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="43">
-        <v>46266</v>
-      </c>
-      <c r="F8" s="44">
-        <v>46353</v>
-      </c>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="50">
-        <v>0.15</v>
-      </c>
-      <c r="E9" s="51">
-        <v>46272</v>
-      </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="53">
-        <v>0.875</v>
-      </c>
-      <c r="H9" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="133">
-        <v>1</v>
-      </c>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="26">
-        <v>0.15</v>
-      </c>
-      <c r="E10" s="27">
-        <v>46272</v>
-      </c>
-      <c r="F10" s="28">
-        <v>46278</v>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="133">
-        <v>4</v>
-      </c>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="27">
-        <v>46274</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="29">
-        <v>0.875</v>
-      </c>
-      <c r="H11" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="133">
-        <v>3</v>
-      </c>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="57">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="66">
-        <v>46274</v>
-      </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="60">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H12" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="133">
-        <v>2</v>
-      </c>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="76"/>
-      <c r="B13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="42">
-        <v>0.1</v>
-      </c>
-      <c r="E13" s="43">
+      <c r="E13" s="126">
         <v>46279</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="127">
         <v>46285</v>
       </c>
-      <c r="G13" s="45"/>
-      <c r="H13" s="46" t="s">
+      <c r="G13" s="128"/>
+      <c r="H13" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="133">
-        <v>5</v>
-      </c>
-      <c r="J13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="69" t="s">
+      <c r="I13" s="131"/>
+      <c r="J13" s="134"/>
+    </row>
+    <row r="14" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="49" t="s">
@@ -2171,23 +2158,25 @@
       <c r="D14" s="50">
         <v>0.1</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="69">
         <v>46288</v>
       </c>
-      <c r="F14" s="52"/>
+      <c r="F14" s="52">
+        <v>46295</v>
+      </c>
       <c r="G14" s="53">
         <v>0.79166666666666663</v>
       </c>
       <c r="H14" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="133">
-        <v>6</v>
+      <c r="I14" s="132">
+        <v>2</v>
       </c>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="71" t="s">
+    <row r="15" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="70" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="56" t="s">
@@ -2204,12 +2193,12 @@
       </c>
       <c r="G15" s="60"/>
       <c r="H15" s="61"/>
-      <c r="I15" s="133">
-        <v>9</v>
+      <c r="I15" s="132">
+        <v>4</v>
       </c>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B16" s="48" t="s">
         <v>11</v>
       </c>
@@ -2229,8 +2218,8 @@
       <c r="H16" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="133">
-        <v>8</v>
+      <c r="I16" s="132">
+        <v>3</v>
       </c>
       <c r="J16" s="20"/>
     </row>
@@ -2254,14 +2243,14 @@
       <c r="H17" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="133">
-        <v>10</v>
+      <c r="I17" s="132">
+        <v>5</v>
       </c>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="76"/>
-      <c r="B18" s="72" t="s">
+      <c r="A18" s="75"/>
+      <c r="B18" s="71" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="49" t="s">
@@ -2278,18 +2267,20 @@
       </c>
       <c r="G18" s="53"/>
       <c r="H18" s="54"/>
-      <c r="I18" s="133"/>
+      <c r="I18" s="132">
+        <v>9</v>
+      </c>
       <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="76"/>
+      <c r="A19" s="75"/>
       <c r="B19" s="65" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="73">
+      <c r="D19" s="72">
         <v>0.1</v>
       </c>
       <c r="E19" s="58">
@@ -2302,7 +2293,9 @@
       <c r="H19" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="133"/>
+      <c r="I19" s="132">
+        <v>6</v>
+      </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
@@ -2325,7 +2318,9 @@
       <c r="H20" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="133"/>
+      <c r="I20" s="132">
+        <v>7</v>
+      </c>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -2348,11 +2343,13 @@
       <c r="H21" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="133"/>
+      <c r="I21" s="132">
+        <v>11</v>
+      </c>
       <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="73" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="49" t="s">
@@ -2371,7 +2368,9 @@
       <c r="H22" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="133"/>
+      <c r="I22" s="132">
+        <v>19</v>
+      </c>
       <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -2394,11 +2393,13 @@
       <c r="H23" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="133"/>
+      <c r="I23" s="132">
+        <v>8</v>
+      </c>
       <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="76"/>
+      <c r="A24" s="75"/>
       <c r="B24" s="48" t="s">
         <v>11</v>
       </c>
@@ -2418,12 +2419,14 @@
       <c r="H24" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="133"/>
+      <c r="I24" s="132">
+        <v>10</v>
+      </c>
       <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="76"/>
-      <c r="B25" s="71" t="s">
+      <c r="A25" s="75"/>
+      <c r="B25" s="70" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="56" t="s">
@@ -2440,11 +2443,13 @@
       </c>
       <c r="G25" s="60"/>
       <c r="H25" s="61"/>
-      <c r="I25" s="133"/>
+      <c r="I25" s="132">
+        <v>15</v>
+      </c>
       <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="74" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="41" t="s">
@@ -2463,7 +2468,9 @@
       <c r="H26" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="133"/>
+      <c r="I26" s="132">
+        <v>12</v>
+      </c>
       <c r="J26" s="21"/>
     </row>
     <row r="27" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
@@ -2486,12 +2493,14 @@
       <c r="H27" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="I27" s="133"/>
+      <c r="I27" s="132">
+        <v>16</v>
+      </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
     </row>
     <row r="28" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -2508,13 +2517,15 @@
         <v>0.49930555555555556</v>
       </c>
       <c r="H28" s="64"/>
-      <c r="I28" s="133"/>
+      <c r="I28" s="132">
+        <v>13</v>
+      </c>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
     </row>
     <row r="29" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="70" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="56" t="s">
@@ -2533,13 +2544,15 @@
       <c r="H29" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="I29" s="133"/>
+      <c r="I29" s="132">
+        <v>14</v>
+      </c>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
     </row>
     <row r="30" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="76"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="62" t="s">
         <v>12</v>
       </c>
@@ -2559,13 +2572,15 @@
       <c r="H30" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="133"/>
+      <c r="I30" s="132">
+        <v>17</v>
+      </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
     </row>
     <row r="31" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="76"/>
+      <c r="A31" s="75"/>
       <c r="B31" s="63" t="s">
         <v>42</v>
       </c>
@@ -2583,14 +2598,16 @@
       </c>
       <c r="G31" s="29"/>
       <c r="H31" s="64"/>
-      <c r="I31" s="133"/>
+      <c r="I31" s="132">
+        <v>18</v>
+      </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
     </row>
     <row r="32" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="76"/>
-      <c r="B32" s="68" t="s">
+      <c r="A32" s="75"/>
+      <c r="B32" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="25" t="s">
@@ -2609,13 +2626,15 @@
       <c r="H32" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="133"/>
+      <c r="I32" s="132">
+        <v>20</v>
+      </c>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
     </row>
     <row r="33" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="76"/>
+      <c r="A33" s="75"/>
       <c r="B33" s="65" t="s">
         <v>13</v>
       </c>
@@ -2635,7 +2654,9 @@
       <c r="H33" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="I33" s="133"/>
+      <c r="I33" s="132">
+        <v>21</v>
+      </c>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
     </row>
@@ -2659,7 +2680,9 @@
       <c r="H34" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="I34" s="133"/>
+      <c r="I34" s="132">
+        <v>22</v>
+      </c>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
     </row>
@@ -2677,7 +2700,7 @@
       <c r="F35" s="28"/>
       <c r="G35" s="29"/>
       <c r="H35" s="30"/>
-      <c r="I35" s="133"/>
+      <c r="I35" s="132"/>
       <c r="J35" s="21"/>
       <c r="L35" s="21"/>
     </row>
@@ -2688,7 +2711,7 @@
       <c r="F36" s="18"/>
       <c r="G36" s="19"/>
       <c r="H36" s="24"/>
-      <c r="I36" s="133"/>
+      <c r="I36" s="132"/>
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.5">
@@ -2724,121 +2747,121 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="90" t="s">
+      <c r="D2" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="77" t="s">
+      <c r="F2" s="76" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="D3" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="94" t="s">
+      <c r="E3" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="95" t="s">
+      <c r="F3" s="94" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="E4" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="100" t="s">
+      <c r="F4" s="99" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="84" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="85" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="F7" s="81" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="83" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D363271-B0B8-443A-AB0C-63EE2574E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABAE2AD-64EC-4CBE-B781-CF4D474B683D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,7 +397,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,6 +464,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -749,7 +755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -887,9 +893,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -924,20 +927,11 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1109,6 +1103,48 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="12" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="12" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1846,7 +1882,7 @@
     <col min="6" max="6" width="38.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="133"/>
+    <col min="9" max="9" width="9.33203125" style="129"/>
     <col min="10" max="10" width="9.33203125" style="14"/>
     <col min="11" max="16384" width="9.33203125" style="2"/>
   </cols>
@@ -1873,384 +1909,384 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="130"/>
+      <c r="I1" s="126"/>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="123" t="s">
+    <row r="2" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="124" t="s">
+      <c r="C2" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="125">
+      <c r="D2" s="121">
         <v>0.2</v>
       </c>
-      <c r="E2" s="126">
+      <c r="E2" s="122">
         <v>46242</v>
       </c>
-      <c r="F2" s="127">
+      <c r="F2" s="123">
         <v>46264</v>
       </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="129" t="s">
+      <c r="G2" s="124"/>
+      <c r="H2" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="131"/>
-      <c r="J2" s="108"/>
-    </row>
-    <row r="3" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="101" t="s">
+      <c r="I2" s="127"/>
+      <c r="J2" s="104"/>
+    </row>
+    <row r="3" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B3" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="102" t="s">
+      <c r="C3" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="103">
+      <c r="D3" s="99">
         <v>0.2</v>
       </c>
-      <c r="E3" s="104">
+      <c r="E3" s="100">
         <v>46246</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106">
+      <c r="F3" s="101"/>
+      <c r="G3" s="102">
         <v>0.99930555555555556</v>
       </c>
-      <c r="H3" s="107" t="s">
+      <c r="H3" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="131"/>
-      <c r="J3" s="108"/>
-    </row>
-    <row r="4" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="55" t="s">
+      <c r="I3" s="127"/>
+      <c r="J3" s="104"/>
+    </row>
+    <row r="4" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="107">
         <v>0.15</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="132">
         <v>46249</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="109">
         <v>46292</v>
       </c>
-      <c r="G4" s="60"/>
-      <c r="H4" s="61" t="s">
+      <c r="G4" s="110"/>
+      <c r="H4" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="132">
+      <c r="I4" s="127">
         <v>1</v>
       </c>
-      <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="101" t="s">
+      <c r="J4" s="104"/>
+    </row>
+    <row r="5" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="102" t="s">
+      <c r="C5" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="103">
+      <c r="D5" s="99">
         <v>0.1</v>
       </c>
-      <c r="E5" s="104">
+      <c r="E5" s="100">
         <v>46251</v>
       </c>
-      <c r="F5" s="105">
+      <c r="F5" s="101">
         <v>46257</v>
       </c>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107" t="s">
+      <c r="G5" s="102"/>
+      <c r="H5" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="131"/>
-      <c r="J5" s="108"/>
-    </row>
-    <row r="6" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="116" t="s">
+      <c r="I5" s="127"/>
+      <c r="J5" s="104"/>
+    </row>
+    <row r="6" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="118">
+      <c r="D6" s="114">
         <v>0.1</v>
       </c>
-      <c r="E6" s="119">
+      <c r="E6" s="115">
         <v>46251</v>
       </c>
-      <c r="F6" s="120">
+      <c r="F6" s="116">
         <v>46257</v>
       </c>
-      <c r="G6" s="121"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="108"/>
-    </row>
-    <row r="7" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="109" t="s">
+      <c r="G6" s="117"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="104"/>
+    </row>
+    <row r="7" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="110" t="s">
+      <c r="C7" s="106" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="111">
+      <c r="D7" s="107">
         <v>0.1</v>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="108">
         <v>46253</v>
       </c>
-      <c r="F7" s="113"/>
-      <c r="G7" s="114">
+      <c r="F7" s="109"/>
+      <c r="G7" s="110">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H7" s="115" t="s">
+      <c r="H7" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="131"/>
-      <c r="J7" s="108"/>
-    </row>
-    <row r="8" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="123" t="s">
+      <c r="I7" s="127"/>
+      <c r="J7" s="104"/>
+    </row>
+    <row r="8" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="125">
+      <c r="D8" s="121">
         <v>0.1</v>
       </c>
-      <c r="E8" s="126">
+      <c r="E8" s="122">
         <v>46266</v>
       </c>
-      <c r="F8" s="127">
+      <c r="F8" s="123">
         <v>46353</v>
       </c>
-      <c r="G8" s="128"/>
-      <c r="H8" s="129"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="108"/>
-    </row>
-    <row r="9" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="101" t="s">
+      <c r="G8" s="124"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="104"/>
+    </row>
+    <row r="9" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="102" t="s">
+      <c r="C9" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="103">
+      <c r="D9" s="99">
         <v>0.15</v>
       </c>
-      <c r="E9" s="104">
+      <c r="E9" s="100">
         <v>46272</v>
       </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="106">
+      <c r="F9" s="101"/>
+      <c r="G9" s="102">
         <v>0.875</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="131"/>
-      <c r="J9" s="108"/>
-    </row>
-    <row r="10" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="116" t="s">
+      <c r="I9" s="127"/>
+      <c r="J9" s="104"/>
+    </row>
+    <row r="10" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B10" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="118">
+      <c r="D10" s="114">
         <v>0.15</v>
       </c>
-      <c r="E10" s="119">
+      <c r="E10" s="115">
         <v>46272</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10" s="116">
         <v>46278</v>
       </c>
-      <c r="G10" s="121"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="108"/>
-    </row>
-    <row r="11" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="116" t="s">
+      <c r="G10" s="117"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="104"/>
+    </row>
+    <row r="11" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="118">
+      <c r="D11" s="114">
         <v>0.1</v>
       </c>
-      <c r="E11" s="119">
+      <c r="E11" s="115">
         <v>46274</v>
       </c>
-      <c r="F11" s="120"/>
-      <c r="G11" s="121">
+      <c r="F11" s="116"/>
+      <c r="G11" s="117">
         <v>0.875</v>
       </c>
-      <c r="H11" s="122" t="s">
+      <c r="H11" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="131"/>
-      <c r="J11" s="108"/>
-    </row>
-    <row r="12" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="109" t="s">
+      <c r="I11" s="127"/>
+      <c r="J11" s="104"/>
+    </row>
+    <row r="12" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="110" t="s">
+      <c r="C12" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="111">
+      <c r="D12" s="107">
         <v>0.15</v>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="108">
         <v>46274</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="114">
+      <c r="F12" s="109"/>
+      <c r="G12" s="110">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H12" s="115" t="s">
+      <c r="H12" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="131"/>
-      <c r="J12" s="108"/>
-    </row>
-    <row r="13" spans="2:10" s="100" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="123" t="s">
+      <c r="I12" s="127"/>
+      <c r="J12" s="104"/>
+    </row>
+    <row r="13" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="124" t="s">
+      <c r="C13" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="125">
+      <c r="D13" s="121">
         <v>0.1</v>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="122">
         <v>46279</v>
       </c>
-      <c r="F13" s="127">
+      <c r="F13" s="123">
         <v>46285</v>
       </c>
-      <c r="G13" s="128"/>
-      <c r="H13" s="129" t="s">
+      <c r="G13" s="124"/>
+      <c r="H13" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="131"/>
-      <c r="J13" s="134"/>
-    </row>
-    <row r="14" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="68" t="s">
+      <c r="I13" s="127"/>
+      <c r="J13" s="130"/>
+    </row>
+    <row r="14" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="99">
         <v>0.1</v>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="134">
         <v>46288</v>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="101">
         <v>46295</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="102">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H14" s="54" t="s">
+      <c r="H14" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="132">
+      <c r="I14" s="127">
         <v>2</v>
       </c>
-      <c r="J14" s="20"/>
-    </row>
-    <row r="15" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="70" t="s">
+      <c r="J14" s="130"/>
+    </row>
+    <row r="15" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="107">
         <v>0.1</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="132">
         <v>46290</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="109">
         <v>46297</v>
       </c>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="132">
+      <c r="G15" s="110"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="127">
         <v>4</v>
       </c>
-      <c r="J15" s="20"/>
-    </row>
-    <row r="16" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="48" t="s">
+      <c r="J15" s="130"/>
+    </row>
+    <row r="16" spans="2:10" s="96" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="99">
         <v>0.2</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="100">
         <v>46295</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="53">
+      <c r="F16" s="101"/>
+      <c r="G16" s="102">
         <v>0.875</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="132">
+      <c r="I16" s="127">
         <v>3</v>
       </c>
-      <c r="J16" s="20"/>
-    </row>
-    <row r="17" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="55" t="s">
+      <c r="J16" s="130"/>
+    </row>
+    <row r="17" spans="1:13" s="96" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="107">
         <v>0.3</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="132">
         <v>46297</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="60">
+      <c r="F17" s="109"/>
+      <c r="G17" s="110">
         <v>0.875</v>
       </c>
-      <c r="H17" s="61" t="s">
+      <c r="H17" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="132">
+      <c r="I17" s="127">
         <v>5</v>
       </c>
-      <c r="J17" s="20"/>
+      <c r="J17" s="130"/>
     </row>
     <row r="18" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="75"/>
-      <c r="B18" s="71" t="s">
+      <c r="A18" s="71"/>
+      <c r="B18" s="68" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="49" t="s">
@@ -2267,39 +2303,38 @@
       </c>
       <c r="G18" s="53"/>
       <c r="H18" s="54"/>
-      <c r="I18" s="132">
+      <c r="I18" s="128">
         <v>9</v>
       </c>
       <c r="J18" s="21"/>
     </row>
-    <row r="19" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="75"/>
-      <c r="B19" s="65" t="s">
+    <row r="19" spans="1:13" s="135" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="146">
         <v>0.1</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="139">
         <v>46302</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="60">
+      <c r="F19" s="140"/>
+      <c r="G19" s="141">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H19" s="61" t="s">
+      <c r="H19" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="132">
+      <c r="I19" s="143">
         <v>6</v>
       </c>
-      <c r="J19" s="21"/>
+      <c r="J19" s="144"/>
     </row>
     <row r="20" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="61" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="49" t="s">
@@ -2318,38 +2353,38 @@
       <c r="H20" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="132">
+      <c r="I20" s="128">
         <v>7</v>
       </c>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="55" t="s">
+    <row r="21" spans="1:13" s="135" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="136" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="138">
         <v>0.15</v>
       </c>
-      <c r="E21" s="58">
+      <c r="E21" s="139">
         <v>46308</v>
       </c>
-      <c r="F21" s="59">
+      <c r="F21" s="140">
         <v>46327</v>
       </c>
-      <c r="G21" s="60"/>
-      <c r="H21" s="61" t="s">
+      <c r="G21" s="141"/>
+      <c r="H21" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="132">
+      <c r="I21" s="143">
         <v>11</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="144"/>
     </row>
     <row r="22" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="69" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="49" t="s">
@@ -2368,38 +2403,38 @@
       <c r="H22" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="132">
+      <c r="I22" s="128">
         <v>19</v>
       </c>
       <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="56">
         <v>0.1</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="57">
         <v>46316</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="60">
+      <c r="F23" s="58"/>
+      <c r="G23" s="59">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H23" s="61" t="s">
+      <c r="H23" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="132">
+      <c r="I23" s="128">
         <v>8</v>
       </c>
       <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="75"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="48" t="s">
         <v>11</v>
       </c>
@@ -2419,37 +2454,37 @@
       <c r="H24" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="132">
+      <c r="I24" s="128">
         <v>10</v>
       </c>
       <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="75"/>
-      <c r="B25" s="70" t="s">
+      <c r="A25" s="71"/>
+      <c r="B25" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="56">
         <v>0.2</v>
       </c>
-      <c r="E25" s="58">
+      <c r="E25" s="57">
         <v>46325</v>
       </c>
-      <c r="F25" s="59">
+      <c r="F25" s="58">
         <v>46341</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="132">
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="128">
         <v>15</v>
       </c>
       <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="70" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="41" t="s">
@@ -2468,13 +2503,13 @@
       <c r="H26" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="132">
+      <c r="I26" s="128">
         <v>12</v>
       </c>
       <c r="J26" s="21"/>
     </row>
     <row r="27" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="61" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="49" t="s">
@@ -2493,14 +2528,14 @@
       <c r="H27" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="I27" s="132">
+      <c r="I27" s="128">
         <v>16</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
     </row>
     <row r="28" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="66" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -2516,8 +2551,8 @@
       <c r="G28" s="29">
         <v>0.49930555555555556</v>
       </c>
-      <c r="H28" s="64"/>
-      <c r="I28" s="132">
+      <c r="H28" s="63"/>
+      <c r="I28" s="128">
         <v>13</v>
       </c>
       <c r="J28" s="16"/>
@@ -2525,26 +2560,26 @@
       <c r="L28" s="16"/>
     </row>
     <row r="29" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="56" t="s">
+      <c r="C29" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="57">
+      <c r="D29" s="56">
         <v>0.2</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="57">
         <v>46336</v>
       </c>
-      <c r="F29" s="59"/>
-      <c r="G29" s="60">
+      <c r="F29" s="58"/>
+      <c r="G29" s="59">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H29" s="61" t="s">
+      <c r="H29" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="I29" s="132">
+      <c r="I29" s="128">
         <v>14</v>
       </c>
       <c r="J29" s="16"/>
@@ -2552,8 +2587,8 @@
       <c r="L29" s="16"/>
     </row>
     <row r="30" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="75"/>
-      <c r="B30" s="62" t="s">
+      <c r="A30" s="71"/>
+      <c r="B30" s="61" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="49" t="s">
@@ -2572,7 +2607,7 @@
       <c r="H30" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="132">
+      <c r="I30" s="128">
         <v>17</v>
       </c>
       <c r="J30" s="21"/>
@@ -2580,8 +2615,8 @@
       <c r="L30" s="21"/>
     </row>
     <row r="31" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="75"/>
-      <c r="B31" s="63" t="s">
+      <c r="A31" s="71"/>
+      <c r="B31" s="62" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="25" t="s">
@@ -2597,8 +2632,8 @@
         <v>46343</v>
       </c>
       <c r="G31" s="29"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="132">
+      <c r="H31" s="63"/>
+      <c r="I31" s="128">
         <v>18</v>
       </c>
       <c r="J31" s="21"/>
@@ -2606,8 +2641,8 @@
       <c r="L31" s="21"/>
     </row>
     <row r="32" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="75"/>
-      <c r="B32" s="67" t="s">
+      <c r="A32" s="71"/>
+      <c r="B32" s="66" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="25" t="s">
@@ -2623,10 +2658,10 @@
       <c r="G32" s="29">
         <v>0.875</v>
       </c>
-      <c r="H32" s="64" t="s">
+      <c r="H32" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="132">
+      <c r="I32" s="128">
         <v>20</v>
       </c>
       <c r="K32" s="21"/>
@@ -2634,27 +2669,27 @@
       <c r="M32" s="22"/>
     </row>
     <row r="33" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="75"/>
-      <c r="B33" s="65" t="s">
+      <c r="A33" s="71"/>
+      <c r="B33" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="C33" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="57">
+      <c r="D33" s="56">
         <v>0.2</v>
       </c>
-      <c r="E33" s="66">
+      <c r="E33" s="65">
         <v>46344</v>
       </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="60">
+      <c r="F33" s="58"/>
+      <c r="G33" s="59">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H33" s="61" t="s">
+      <c r="H33" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="I33" s="132">
+      <c r="I33" s="128">
         <v>21</v>
       </c>
       <c r="K33" s="21"/>
@@ -2680,7 +2715,7 @@
       <c r="H34" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="I34" s="132">
+      <c r="I34" s="128">
         <v>22</v>
       </c>
       <c r="K34" s="21"/>
@@ -2700,7 +2735,7 @@
       <c r="F35" s="28"/>
       <c r="G35" s="29"/>
       <c r="H35" s="30"/>
-      <c r="I35" s="132"/>
+      <c r="I35" s="128"/>
       <c r="J35" s="21"/>
       <c r="L35" s="21"/>
     </row>
@@ -2711,7 +2746,7 @@
       <c r="F36" s="18"/>
       <c r="G36" s="19"/>
       <c r="H36" s="24"/>
-      <c r="I36" s="132"/>
+      <c r="I36" s="128"/>
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.5">
@@ -2747,121 +2782,121 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="72" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="94" t="s">
+      <c r="F3" s="90" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="92" t="s">
+      <c r="D4" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="99" t="s">
+      <c r="F4" s="95" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="84" t="s">
+      <c r="F5" s="80" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="81" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="77" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="82" t="s">
+      <c r="C8" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="83" t="s">
+      <c r="F8" s="79" t="s">
         <v>69</v>
       </c>
     </row>
